--- a/Result/profitability/6126.xlsx
+++ b/Result/profitability/6126.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1887500000000001</v>
+        <v>0.1925000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>23.235</v>
+        <v>22.66375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1725</v>
+        <v>0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>23.345</v>
+        <v>22.91625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.22875</v>
+        <v>0.2225</v>
       </c>
       <c r="N4" t="n">
-        <v>23.85375</v>
+        <v>23.25375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22375</v>
+        <v>0.2200000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>23.6075</v>
+        <v>22.70625</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2525000000000001</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.17875</v>
+        <v>22.43875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2837500000000001</v>
+        <v>0.3025</v>
       </c>
       <c r="N7" t="n">
-        <v>23.68375</v>
+        <v>23.02375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.485</v>
+        <v>0.465</v>
       </c>
       <c r="N8" t="n">
-        <v>24.80875</v>
+        <v>24.4475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6126</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1604</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1318</v>
+      </c>
+      <c r="E75" t="n">
+        <v>286</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>84</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>71</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2075000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.1125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.889999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1393442622950818</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1363636363636364</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.209999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2877094972067038</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
